--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484598_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484598_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7272</v>
+        <v>3.4507</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9198</v>
+        <v>3.4507</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8074</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1719</v>
+        <v>3.4507</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6233</v>
+        <v>0.3251</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5486</v>
+        <v>3.1256</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5615</v>
+        <v>3.4507</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9165</v>
+        <v>0.3251</v>
       </c>
       <c r="L2" t="n">
-        <v>1.645</v>
+        <v>3.1256</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3896</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2932</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0964</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8381</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0234</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8147</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4507</v>
+        <v>3.4367</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4507</v>
+        <v>1.9961</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.4406</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4507</v>
+        <v>1.5333</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3251</v>
+        <v>-0.6341</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1256</v>
+        <v>2.1674</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4507</v>
+        <v>2.4128</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3251</v>
+        <v>0.3094</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1256</v>
+        <v>2.1034</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.9434</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.3348</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.4559</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2471</v>
+        <v>2.7996</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7161</v>
+        <v>1.1942</v>
       </c>
       <c r="F4" t="n">
-        <v>1.531</v>
+        <v>1.6054</v>
       </c>
       <c r="G4" t="n">
         <v>3.5281</v>
@@ -766,13 +766,13 @@
         <v>2.0158</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4704</v>
+        <v>0.0228</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3643</v>
+        <v>-0.1576</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1061</v>
+        <v>0.1804</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9346</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>M. GARRIDO TALENS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,37 +799,37 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6531</v>
+        <v>2.7273</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4602</v>
+        <v>2.4509</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1929</v>
+        <v>0.2764</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5333</v>
+        <v>1.9147</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6341</v>
+        <v>-0.1337</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1674</v>
+        <v>2.0484</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4128</v>
+        <v>2.4705</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3094</v>
+        <v>0.486</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1034</v>
+        <v>1.9845</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.5558</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9434</v>
+        <v>-0.6198</v>
       </c>
       <c r="O5" t="n">
         <v>0.064</v>
@@ -838,34 +838,34 @@
         <v>1.2828</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1991</v>
+        <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1184</v>
+        <v>0.4853</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9917</v>
+        <v>-0.0196</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1267</v>
+        <v>0.5049</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9554</v>
+        <v>-0.9554</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2151</v>
+        <v>2.5948</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2401</v>
+        <v>0.1095</v>
       </c>
       <c r="F6" t="n">
-        <v>0.975</v>
+        <v>2.4854</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9596</v>
+        <v>3.1719</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9606</v>
+        <v>1.6233</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9202</v>
+        <v>1.5486</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4618</v>
+        <v>3.5615</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4522</v>
+        <v>1.9165</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.9903</v>
+        <v>1.645</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4214</v>
+        <v>-0.3896</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4916</v>
+        <v>-0.2932</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.0964</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6493</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>2.3823</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2034</v>
+        <v>0.7057</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4563</v>
+        <v>0.2131</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7471</v>
+        <v>0.4926</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GARRIDO TALENS</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9959</v>
+        <v>2.3708</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0663</v>
+        <v>1.5006</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0704</v>
+        <v>0.8702</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9147</v>
+        <v>1.1155</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1337</v>
+        <v>0.054</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0484</v>
+        <v>1.0616</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4705</v>
+        <v>1.6484</v>
       </c>
       <c r="K7" t="n">
-        <v>0.486</v>
+        <v>0.8111</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9845</v>
+        <v>0.8373</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5558</v>
+        <v>-0.5329</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6198</v>
+        <v>-0.7572</v>
       </c>
       <c r="O7" t="n">
-        <v>0.064</v>
+        <v>0.2243</v>
       </c>
       <c r="P7" t="n">
         <v>1.2828</v>
@@ -1000,28 +1000,28 @@
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2461</v>
+        <v>-0.0275</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4042</v>
+        <v>-0.1478</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1581</v>
+        <v>0.1203</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8625</v>
+        <v>2.1521</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1521</v>
+        <v>1.1028</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7104</v>
+        <v>1.0493</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.868</v>
+        <v>-0.9596</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5202</v>
+        <v>0.9606</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3882</v>
+        <v>-1.9202</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1151</v>
+        <v>0.4618</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1888</v>
+        <v>1.4522</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.0737</v>
+        <v>-0.9903</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9831</v>
+        <v>-1.4214</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6686</v>
+        <v>-0.4916</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3145</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2069</v>
+        <v>1.1405</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6026</v>
+        <v>0.319</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6043</v>
+        <v>0.8214</v>
       </c>
       <c r="V8" t="n">
-        <v>1.89</v>
+        <v>0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8265</v>
+        <v>1.0345</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0059</v>
+        <v>-0.0813</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8206</v>
+        <v>1.1158</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1155</v>
+        <v>-1.868</v>
       </c>
       <c r="H9" t="n">
-        <v>0.054</v>
+        <v>0.5202</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0616</v>
+        <v>-2.3882</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6484</v>
+        <v>0.1151</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8111</v>
+        <v>1.1888</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8373</v>
+        <v>-1.0737</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5329</v>
+        <v>-1.9831</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7572</v>
+        <v>-0.6686</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2243</v>
+        <v>-1.3145</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5718</v>
+        <v>1.379</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6425</v>
+        <v>0.3692</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0707</v>
+        <v>1.0098</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="10">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4926</v>
+        <v>0.6631</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8682</v>
+        <v>0.9644</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3756</v>
+        <v>-0.3013</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9755</v>
@@ -1312,13 +1312,13 @@
         <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>0.269</v>
+        <v>0.4395</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1485</v>
+        <v>-0.0524</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4176</v>
+        <v>0.4919</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6335</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8827</v>
+        <v>-0.0718</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.0655</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1301</v>
+        <v>-0.0063</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0671</v>
@@ -1390,13 +1390,13 @@
         <v>2.1991</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1271</v>
+        <v>-0.3162</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.138</v>
+        <v>-0.451</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0109</v>
+        <v>0.1348</v>
       </c>
       <c r="V12" t="n">
         <v>0.945</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.05</v>
+        <v>-4.0692</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7232</v>
+        <v>-2.6681</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3268</v>
+        <v>-1.4011</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5291</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6465</v>
+        <v>0.6273</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0565</v>
+        <v>-0.0015</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.6288</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.5133</v>
+        <v>18.0639</v>
       </c>
       <c r="E14" t="n">
-        <v>10.379</v>
+        <v>10.9296</v>
       </c>
       <c r="F14" t="n">
-        <v>7.134399999999998</v>
+        <v>7.134400000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>6.290200000000002</v>
+        <v>6.2902</v>
       </c>
       <c r="H14" t="n">
         <v>3.403500000000001</v>
@@ -1534,7 +1534,7 @@
         <v>-5.6487</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.6115</v>
+        <v>-5.611499999999999</v>
       </c>
       <c r="P14" t="n">
         <v>7.3303</v>
@@ -1546,10 +1546,10 @@
         <v>17.4094</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5709</v>
+        <v>4.121599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9347999999999997</v>
+        <v>-0.3845000000000001</v>
       </c>
       <c r="U14" t="n">
         <v>4.5059</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5428</v>
+        <v>1.9012</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4436</v>
+        <v>1.3474</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0992</v>
+        <v>0.5538</v>
       </c>
       <c r="G15" t="n">
         <v>2.8691</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6379</v>
+        <v>-0.2794</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3688</v>
+        <v>-0.4649</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2691</v>
+        <v>0.1855</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3219</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0869</v>
+        <v>1.1335</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3112</v>
+        <v>2.4073</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2243</v>
+        <v>-1.2738</v>
       </c>
       <c r="G16" t="n">
         <v>1.2112</v>
@@ -1702,13 +1702,13 @@
         <v>0.1833</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3075</v>
+        <v>-0.2609</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4404</v>
+        <v>-0.3443</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1329</v>
+        <v>0.0833</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.338</v>
+        <v>-0.3497</v>
       </c>
       <c r="E17" t="n">
         <v>0.5073</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8452</v>
+        <v>-0.857</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6332</v>
@@ -1780,13 +1780,13 @@
         <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>0.324</v>
+        <v>0.3122</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4608</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7847</v>
+        <v>0.773</v>
       </c>
       <c r="V17" t="n">
         <v>-0.945</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. VIDAL BALDOVI</t>
+          <t>S. LOZANO CATALA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.413</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4753</v>
+        <v>-1.4899</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9376</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0055</v>
+        <v>-0.4597</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2005</v>
+        <v>-0.0525</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.805</v>
+        <v>-0.4072</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1929</v>
+        <v>-0.4168</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4329</v>
+        <v>0.1826</v>
       </c>
       <c r="L18" t="n">
-        <v>0.76</v>
+        <v>-0.5994</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.1983</v>
+        <v>-0.043</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6333</v>
+        <v>-0.2351</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.565</v>
+        <v>0.1922</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6084</v>
+        <v>-0.151</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1252</v>
+        <v>-0.1568</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4831</v>
+        <v>0.0058</v>
       </c>
       <c r="V18" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LOZANO CATALA</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5208</v>
+        <v>-1.5046</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6822</v>
+        <v>-0.2429</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1615</v>
+        <v>-1.2617</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4597</v>
+        <v>0.4905</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0525</v>
+        <v>-0.2854</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4072</v>
+        <v>0.7759</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4168</v>
+        <v>0.8524</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1826</v>
+        <v>0.1084</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5994</v>
+        <v>0.7441</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.043</v>
+        <v>-0.362</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2351</v>
+        <v>-0.3938</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1922</v>
+        <v>0.0318</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3665</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6945</v>
+        <v>-0.1784</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3492</v>
+        <v>-0.1791</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3453</v>
+        <v>0.0007</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.799</v>
+        <v>-2.1892</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3391</v>
+        <v>-1.0753</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4599</v>
+        <v>-1.1139</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4905</v>
+        <v>-0.4377</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2854</v>
+        <v>0.4505</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7759</v>
+        <v>-0.8882</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8524</v>
+        <v>1.289</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1084</v>
+        <v>1.2473</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7441</v>
+        <v>0.0417</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.362</v>
+        <v>-1.7267</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3938</v>
+        <v>-0.7968</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0318</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5498</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4727</v>
+        <v>0.5313</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2753</v>
+        <v>0.0626</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1974</v>
+        <v>0.4687</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>S. VIDAL BALDOVI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.402</v>
+        <v>-2.3703</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.883</v>
+        <v>-1.1484</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.519</v>
+        <v>-1.2219</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4377</v>
+        <v>-3.0055</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4505</v>
+        <v>-1.2005</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8882</v>
+        <v>-1.805</v>
       </c>
       <c r="J21" t="n">
-        <v>1.289</v>
+        <v>1.1929</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2473</v>
+        <v>0.4329</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0417</v>
+        <v>0.76</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7267</v>
+        <v>-4.1983</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7968</v>
+        <v>-1.6333</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-2.565</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6493</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3186</v>
+        <v>0.651</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2549</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0636</v>
+        <v>1.1989</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>0.9554</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9554</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9114</v>
+        <v>-2.5661</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0423</v>
+        <v>-1.85</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.869</v>
+        <v>-0.716</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8389</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1562</v>
+        <v>-0.8109</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8808</v>
+        <v>-0.6885</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2754</v>
+        <v>-0.1224</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2044</v>
+        <v>-2.8096</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7752</v>
+        <v>-2.5829</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4292</v>
+        <v>-0.2267</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7148</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0681</v>
+        <v>-0.6733</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0279</v>
+        <v>-0.8356</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0402</v>
+        <v>0.1623</v>
       </c>
       <c r="V23" t="n">
         <v>0.3115</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.229</v>
+        <v>-2.856</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8224</v>
+        <v>-1.7263</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4066</v>
+        <v>-1.1297</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9088000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4876</v>
+        <v>-0.1146</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5324</v>
+        <v>-0.4363</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0448</v>
+        <v>0.3216</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3257</v>
+        <v>-3.0023</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3769</v>
+        <v>-1.2807</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9489</v>
+        <v>-1.7216</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8624</v>
@@ -2404,13 +2404,13 @@
         <v>0.1833</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9973</v>
+        <v>-0.6738</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5505</v>
+        <v>-0.4544</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4468</v>
+        <v>-0.2195</v>
       </c>
       <c r="V25" t="n">
         <v>1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.5136</v>
+        <v>-15.5904</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.134300000000001</v>
+        <v>-7.134399999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.379</v>
+        <v>-8.4559</v>
       </c>
       <c r="G26" t="n">
         <v>-6.2902</v>
@@ -2467,13 +2467,13 @@
         <v>-17.5505</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.052000000000001</v>
+        <v>-9.052</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.4986</v>
+        <v>-8.498599999999998</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.330199999999999</v>
+        <v>-7.3302</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.4097</v>
@@ -2482,13 +2482,13 @@
         <v>10.0793</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.5708</v>
+        <v>-1.6478</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.506</v>
+        <v>-4.505999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9349000000000002</v>
+        <v>2.8579</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3218999999999999</v>
